--- a/data/sars/pacific/tables/Pacific_2019_Appendix2.xlsx
+++ b/data/sars/pacific/tables/Pacific_2019_Appendix2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cfree/Dropbox/Chris/UCSB/projects/marine_mammals/us_sar_synthesis/data/sars/pacific/tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FD5C9E3-56D1-2049-9245-5E0FC77D3035}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3CD4AEF-0B1C-264E-B6F3-91F6D29C0540}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="120" yWindow="500" windowWidth="31260" windowHeight="20180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="Table 1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Table 1'!$A$1:$N$88</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Table 1'!$A$1:$P$88</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="137">
   <si>
     <t>California Sea Lion (U.S.)</t>
   </si>
@@ -415,10 +415,25 @@
     <t>survey3</t>
   </si>
   <si>
-    <t>revised</t>
-  </si>
-  <si>
     <t>Sperm whale (California/Oregon/Washington)</t>
+  </si>
+  <si>
+    <t>otes</t>
+  </si>
+  <si>
+    <t>notes</t>
+  </si>
+  <si>
+    <t>RF=0.2 in SAR; RF=0.1 was typo in table</t>
+  </si>
+  <si>
+    <t>revision_yr</t>
+  </si>
+  <si>
+    <t>revised_yn</t>
+  </si>
+  <si>
+    <t>yes</t>
   </si>
 </sst>
 </file>
@@ -835,25 +850,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N88"/>
+  <dimension ref="A1:P88"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="70.19921875" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.19921875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.19921875" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.19921875" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.59765625" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.796875" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.19921875" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.19921875" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.59765625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.796875" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="8" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.19921875" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.3984375" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="9.3984375" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.59765625" style="2" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9" style="2"/>
+    <col min="8" max="8" width="13" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.19921875" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.3984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="12.3984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.59765625" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.59765625" style="2" customWidth="1"/>
+    <col min="16" max="16" width="40.59765625" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:16" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>117</v>
       </c>
@@ -894,10 +911,16 @@
         <v>129</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+        <v>134</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -940,8 +963,9 @@
       <c r="N2" s="9">
         <v>2018</v>
       </c>
-    </row>
-    <row r="3" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O2" s="9"/>
+    </row>
+    <row r="3" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -984,8 +1008,9 @@
       <c r="N3" s="9">
         <v>2014</v>
       </c>
-    </row>
-    <row r="4" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O3" s="9"/>
+    </row>
+    <row r="4" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -1024,8 +1049,9 @@
       <c r="N4" s="9">
         <v>2013</v>
       </c>
-    </row>
-    <row r="5" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O4" s="9"/>
+    </row>
+    <row r="5" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
@@ -1064,8 +1090,9 @@
       <c r="N5" s="9">
         <v>2013</v>
       </c>
-    </row>
-    <row r="6" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O5" s="9"/>
+    </row>
+    <row r="6" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
@@ -1104,8 +1131,9 @@
       <c r="N6" s="9">
         <v>2013</v>
       </c>
-    </row>
-    <row r="7" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O6" s="9"/>
+    </row>
+    <row r="7" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A7" s="1" t="s">
         <v>11</v>
       </c>
@@ -1144,13 +1172,14 @@
       <c r="N7" s="9">
         <v>2013</v>
       </c>
-    </row>
-    <row r="8" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O7" s="9"/>
+    </row>
+    <row r="8" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A8" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="7">
-        <v>179000</v>
+      <c r="B8" s="7" t="s">
+        <v>131</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>1</v>
@@ -1188,8 +1217,9 @@
       <c r="N8" s="9">
         <v>2014</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O8" s="9"/>
+    </row>
+    <row r="9" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A9" s="4" t="s">
         <v>13</v>
       </c>
@@ -1232,8 +1262,11 @@
       <c r="N9" s="14">
         <v>2019</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O9" s="14" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A10" s="1" t="s">
         <v>17</v>
       </c>
@@ -1276,8 +1309,9 @@
       <c r="N10" s="9">
         <v>2015</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O10" s="9"/>
+    </row>
+    <row r="11" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A11" s="4" t="s">
         <v>19</v>
       </c>
@@ -1320,8 +1354,11 @@
       <c r="N11" s="14">
         <v>2019</v>
       </c>
-    </row>
-    <row r="12" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O11" s="14" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A12" s="4" t="s">
         <v>22</v>
       </c>
@@ -1364,8 +1401,11 @@
       <c r="N12" s="14">
         <v>2019</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O12" s="14" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A13" s="4" t="s">
         <v>25</v>
       </c>
@@ -1408,8 +1448,11 @@
       <c r="N13" s="14">
         <v>2019</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O13" s="14" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A14" s="4" t="s">
         <v>26</v>
       </c>
@@ -1452,8 +1495,11 @@
       <c r="N14" s="14">
         <v>2019</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O14" s="14" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A15" s="4" t="s">
         <v>28</v>
       </c>
@@ -1496,8 +1542,11 @@
       <c r="N15" s="14">
         <v>2019</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O15" s="14" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A16" s="1" t="s">
         <v>29</v>
       </c>
@@ -1540,8 +1589,9 @@
       <c r="N16" s="9">
         <v>2013</v>
       </c>
-    </row>
-    <row r="17" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O16" s="9"/>
+    </row>
+    <row r="17" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A17" s="1" t="s">
         <v>30</v>
       </c>
@@ -1584,8 +1634,9 @@
       <c r="N17" s="9">
         <v>2016</v>
       </c>
-    </row>
-    <row r="18" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O17" s="9"/>
+    </row>
+    <row r="18" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A18" s="1" t="s">
         <v>32</v>
       </c>
@@ -1628,8 +1679,9 @@
       <c r="N18" s="9">
         <v>2016</v>
       </c>
-    </row>
-    <row r="19" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O18" s="9"/>
+    </row>
+    <row r="19" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A19" s="1" t="s">
         <v>33</v>
       </c>
@@ -1672,8 +1724,9 @@
       <c r="N19" s="9">
         <v>2016</v>
       </c>
-    </row>
-    <row r="20" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O19" s="9"/>
+    </row>
+    <row r="20" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A20" s="1" t="s">
         <v>34</v>
       </c>
@@ -1716,8 +1769,9 @@
       <c r="N20" s="9">
         <v>2016</v>
       </c>
-    </row>
-    <row r="21" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O20" s="9"/>
+    </row>
+    <row r="21" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A21" s="1" t="s">
         <v>36</v>
       </c>
@@ -1760,8 +1814,9 @@
       <c r="N21" s="9">
         <v>2016</v>
       </c>
-    </row>
-    <row r="22" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O21" s="9"/>
+    </row>
+    <row r="22" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A22" s="1" t="s">
         <v>38</v>
       </c>
@@ -1804,8 +1859,9 @@
       <c r="N22" s="9">
         <v>2016</v>
       </c>
-    </row>
-    <row r="23" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O22" s="9"/>
+    </row>
+    <row r="23" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A23" s="1" t="s">
         <v>39</v>
       </c>
@@ -1848,8 +1904,9 @@
       <c r="N23" s="9">
         <v>2016</v>
       </c>
-    </row>
-    <row r="24" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O23" s="9"/>
+    </row>
+    <row r="24" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A24" s="1" t="s">
         <v>40</v>
       </c>
@@ -1892,8 +1949,9 @@
       <c r="N24" s="9">
         <v>2016</v>
       </c>
-    </row>
-    <row r="25" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O24" s="9"/>
+    </row>
+    <row r="25" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A25" s="1" t="s">
         <v>42</v>
       </c>
@@ -1936,8 +1994,9 @@
       <c r="N25" s="9">
         <v>2016</v>
       </c>
-    </row>
-    <row r="26" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O25" s="9"/>
+    </row>
+    <row r="26" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A26" s="1" t="s">
         <v>45</v>
       </c>
@@ -1980,8 +2039,9 @@
       <c r="N26" s="9">
         <v>2016</v>
       </c>
-    </row>
-    <row r="27" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O26" s="9"/>
+    </row>
+    <row r="27" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A27" s="1" t="s">
         <v>46</v>
       </c>
@@ -2024,8 +2084,9 @@
       <c r="N27" s="9">
         <v>2018</v>
       </c>
-    </row>
-    <row r="28" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O27" s="9"/>
+    </row>
+    <row r="28" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A28" s="4" t="s">
         <v>47</v>
       </c>
@@ -2068,8 +2129,11 @@
       <c r="N28" s="14">
         <v>2019</v>
       </c>
-    </row>
-    <row r="29" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O28" s="14" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A29" s="1" t="s">
         <v>48</v>
       </c>
@@ -2112,8 +2176,9 @@
       <c r="N29" s="9">
         <v>2016</v>
       </c>
-    </row>
-    <row r="30" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O29" s="9"/>
+    </row>
+    <row r="30" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A30" s="1" t="s">
         <v>49</v>
       </c>
@@ -2156,8 +2221,9 @@
       <c r="N30" s="9">
         <v>2017</v>
       </c>
-    </row>
-    <row r="31" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O30" s="9"/>
+    </row>
+    <row r="31" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A31" s="1" t="s">
         <v>50</v>
       </c>
@@ -2200,8 +2266,9 @@
       <c r="N31" s="9">
         <v>2017</v>
       </c>
-    </row>
-    <row r="32" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O31" s="9"/>
+    </row>
+    <row r="32" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A32" s="1" t="s">
         <v>51</v>
       </c>
@@ -2244,8 +2311,9 @@
       <c r="N32" s="9">
         <v>2017</v>
       </c>
-    </row>
-    <row r="33" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O32" s="9"/>
+    </row>
+    <row r="33" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A33" s="1" t="s">
         <v>53</v>
       </c>
@@ -2288,8 +2356,9 @@
       <c r="N33" s="9">
         <v>2016</v>
       </c>
-    </row>
-    <row r="34" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O33" s="9"/>
+    </row>
+    <row r="34" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A34" s="1" t="s">
         <v>54</v>
       </c>
@@ -2332,10 +2401,11 @@
       <c r="N34" s="9">
         <v>2016</v>
       </c>
-    </row>
-    <row r="35" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="O34" s="9"/>
+    </row>
+    <row r="35" spans="1:15" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B35" s="6">
         <v>1997</v>
@@ -2376,8 +2446,11 @@
       <c r="N35" s="4">
         <v>2019</v>
       </c>
-    </row>
-    <row r="36" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O35" s="14" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A36" s="1" t="s">
         <v>55</v>
       </c>
@@ -2420,8 +2493,9 @@
       <c r="N36" s="9">
         <v>2018</v>
       </c>
-    </row>
-    <row r="37" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O36" s="9"/>
+    </row>
+    <row r="37" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A37" s="1" t="s">
         <v>56</v>
       </c>
@@ -2464,8 +2538,9 @@
       <c r="N37" s="9">
         <v>2018</v>
       </c>
-    </row>
-    <row r="38" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O37" s="9"/>
+    </row>
+    <row r="38" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A38" s="4" t="s">
         <v>57</v>
       </c>
@@ -2508,8 +2583,11 @@
       <c r="N38" s="14">
         <v>2019</v>
       </c>
-    </row>
-    <row r="39" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O38" s="14" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A39" s="4" t="s">
         <v>60</v>
       </c>
@@ -2552,8 +2630,11 @@
       <c r="N39" s="14">
         <v>2019</v>
       </c>
-    </row>
-    <row r="40" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O39" s="14" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A40" s="1" t="s">
         <v>62</v>
       </c>
@@ -2596,8 +2677,9 @@
       <c r="N40" s="9">
         <v>2018</v>
       </c>
-    </row>
-    <row r="41" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O40" s="9"/>
+    </row>
+    <row r="41" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A41" s="1" t="s">
         <v>65</v>
       </c>
@@ -2640,8 +2722,9 @@
       <c r="N41" s="9">
         <v>2018</v>
       </c>
-    </row>
-    <row r="42" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O41" s="9"/>
+    </row>
+    <row r="42" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A42" s="1" t="s">
         <v>67</v>
       </c>
@@ -2684,8 +2767,9 @@
       <c r="N42" s="9">
         <v>2016</v>
       </c>
-    </row>
-    <row r="43" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O42" s="9"/>
+    </row>
+    <row r="43" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A43" s="1" t="s">
         <v>69</v>
       </c>
@@ -2728,8 +2812,9 @@
       <c r="N43" s="9">
         <v>2015</v>
       </c>
-    </row>
-    <row r="44" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O43" s="9"/>
+    </row>
+    <row r="44" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A44" s="1" t="s">
         <v>70</v>
       </c>
@@ -2770,8 +2855,9 @@
       <c r="N44" s="9">
         <v>2017</v>
       </c>
-    </row>
-    <row r="45" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O44" s="9"/>
+    </row>
+    <row r="45" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A45" s="1" t="s">
         <v>71</v>
       </c>
@@ -2814,8 +2900,9 @@
       <c r="N45" s="9">
         <v>2010</v>
       </c>
-    </row>
-    <row r="46" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O45" s="9"/>
+    </row>
+    <row r="46" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A46" s="1" t="s">
         <v>72</v>
       </c>
@@ -2856,8 +2943,9 @@
       <c r="N46" s="9">
         <v>2017</v>
       </c>
-    </row>
-    <row r="47" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O46" s="9"/>
+    </row>
+    <row r="47" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A47" s="1" t="s">
         <v>73</v>
       </c>
@@ -2898,8 +2986,9 @@
       <c r="N47" s="9">
         <v>2017</v>
       </c>
-    </row>
-    <row r="48" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O47" s="9"/>
+    </row>
+    <row r="48" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A48" s="1" t="s">
         <v>74</v>
       </c>
@@ -2942,8 +3031,9 @@
       <c r="N48" s="9">
         <v>2017</v>
       </c>
-    </row>
-    <row r="49" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O48" s="9"/>
+    </row>
+    <row r="49" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A49" s="1" t="s">
         <v>75</v>
       </c>
@@ -2986,8 +3076,9 @@
       <c r="N49" s="9">
         <v>2017</v>
       </c>
-    </row>
-    <row r="50" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O49" s="9"/>
+    </row>
+    <row r="50" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A50" s="1" t="s">
         <v>76</v>
       </c>
@@ -3030,8 +3121,9 @@
       <c r="N50" s="9">
         <v>2017</v>
       </c>
-    </row>
-    <row r="51" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O50" s="9"/>
+    </row>
+    <row r="51" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A51" s="1" t="s">
         <v>77</v>
       </c>
@@ -3074,8 +3166,9 @@
       <c r="N51" s="9">
         <v>2017</v>
       </c>
-    </row>
-    <row r="52" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O51" s="9"/>
+    </row>
+    <row r="52" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A52" s="1" t="s">
         <v>78</v>
       </c>
@@ -3116,8 +3209,9 @@
       <c r="N52" s="9">
         <v>2017</v>
       </c>
-    </row>
-    <row r="53" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O52" s="9"/>
+    </row>
+    <row r="53" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A53" s="1" t="s">
         <v>79</v>
       </c>
@@ -3156,8 +3250,9 @@
       <c r="N53" s="9">
         <v>2017</v>
       </c>
-    </row>
-    <row r="54" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O53" s="9"/>
+    </row>
+    <row r="54" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A54" s="1" t="s">
         <v>80</v>
       </c>
@@ -3196,8 +3291,9 @@
       <c r="N54" s="9">
         <v>2017</v>
       </c>
-    </row>
-    <row r="55" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O54" s="9"/>
+    </row>
+    <row r="55" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A55" s="1" t="s">
         <v>81</v>
       </c>
@@ -3236,8 +3332,9 @@
       <c r="N55" s="9">
         <v>2017</v>
       </c>
-    </row>
-    <row r="56" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O55" s="9"/>
+    </row>
+    <row r="56" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A56" s="1" t="s">
         <v>82</v>
       </c>
@@ -3278,8 +3375,9 @@
       <c r="N56" s="9">
         <v>2018</v>
       </c>
-    </row>
-    <row r="57" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O56" s="9"/>
+    </row>
+    <row r="57" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A57" s="1" t="s">
         <v>83</v>
       </c>
@@ -3322,8 +3420,9 @@
       <c r="N57" s="9">
         <v>2018</v>
       </c>
-    </row>
-    <row r="58" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O57" s="9"/>
+    </row>
+    <row r="58" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A58" s="1" t="s">
         <v>85</v>
       </c>
@@ -3366,8 +3465,9 @@
       <c r="N58" s="9">
         <v>2018</v>
       </c>
-    </row>
-    <row r="59" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O58" s="9"/>
+    </row>
+    <row r="59" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A59" s="1" t="s">
         <v>87</v>
       </c>
@@ -3410,8 +3510,9 @@
       <c r="N59" s="9">
         <v>2018</v>
       </c>
-    </row>
-    <row r="60" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O59" s="9"/>
+    </row>
+    <row r="60" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A60" s="1" t="s">
         <v>88</v>
       </c>
@@ -3452,8 +3553,9 @@
       <c r="N60" s="9">
         <v>2018</v>
       </c>
-    </row>
-    <row r="61" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O60" s="9"/>
+    </row>
+    <row r="61" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A61" s="1" t="s">
         <v>89</v>
       </c>
@@ -3492,8 +3594,9 @@
       <c r="N61" s="9">
         <v>2018</v>
       </c>
-    </row>
-    <row r="62" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O61" s="9"/>
+    </row>
+    <row r="62" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A62" s="1" t="s">
         <v>90</v>
       </c>
@@ -3532,8 +3635,9 @@
       <c r="N62" s="9">
         <v>2010</v>
       </c>
-    </row>
-    <row r="63" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O62" s="9"/>
+    </row>
+    <row r="63" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A63" s="1" t="s">
         <v>91</v>
       </c>
@@ -3574,8 +3678,9 @@
       <c r="N63" s="9">
         <v>2017</v>
       </c>
-    </row>
-    <row r="64" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O63" s="9"/>
+    </row>
+    <row r="64" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A64" s="1" t="s">
         <v>92</v>
       </c>
@@ -3616,8 +3721,9 @@
       <c r="N64" s="9">
         <v>2017</v>
       </c>
-    </row>
-    <row r="65" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O64" s="9"/>
+    </row>
+    <row r="65" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A65" s="1" t="s">
         <v>93</v>
       </c>
@@ -3658,8 +3764,9 @@
       <c r="N65" s="9">
         <v>2017</v>
       </c>
-    </row>
-    <row r="66" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O65" s="9"/>
+    </row>
+    <row r="66" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A66" s="1" t="s">
         <v>94</v>
       </c>
@@ -3698,8 +3805,9 @@
       <c r="N66" s="9">
         <v>2013</v>
       </c>
-    </row>
-    <row r="67" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O66" s="9"/>
+    </row>
+    <row r="67" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A67" s="1" t="s">
         <v>95</v>
       </c>
@@ -3740,8 +3848,9 @@
       <c r="N67" s="9">
         <v>2017</v>
       </c>
-    </row>
-    <row r="68" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O67" s="9"/>
+    </row>
+    <row r="68" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A68" s="1" t="s">
         <v>96</v>
       </c>
@@ -3780,8 +3889,9 @@
       <c r="N68" s="9">
         <v>2017</v>
       </c>
-    </row>
-    <row r="69" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O68" s="9"/>
+    </row>
+    <row r="69" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A69" s="1" t="s">
         <v>97</v>
       </c>
@@ -3822,8 +3932,9 @@
       <c r="N69" s="9">
         <v>2017</v>
       </c>
-    </row>
-    <row r="70" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O69" s="9"/>
+    </row>
+    <row r="70" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A70" s="1" t="s">
         <v>98</v>
       </c>
@@ -3862,8 +3973,9 @@
       <c r="N70" s="9">
         <v>2012</v>
       </c>
-    </row>
-    <row r="71" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O70" s="9"/>
+    </row>
+    <row r="71" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A71" s="1" t="s">
         <v>99</v>
       </c>
@@ -3906,8 +4018,9 @@
       <c r="N71" s="9">
         <v>2017</v>
       </c>
-    </row>
-    <row r="72" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O71" s="9"/>
+    </row>
+    <row r="72" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A72" s="1" t="s">
         <v>100</v>
       </c>
@@ -3950,8 +4063,9 @@
       <c r="N72" s="9">
         <v>2010</v>
       </c>
-    </row>
-    <row r="73" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O72" s="9"/>
+    </row>
+    <row r="73" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A73" s="1" t="s">
         <v>101</v>
       </c>
@@ -3992,8 +4106,9 @@
       <c r="N73" s="9">
         <v>2017</v>
       </c>
-    </row>
-    <row r="74" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O73" s="9"/>
+    </row>
+    <row r="74" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A74" s="1" t="s">
         <v>102</v>
       </c>
@@ -4034,8 +4149,9 @@
       <c r="N74" s="9">
         <v>2017</v>
       </c>
-    </row>
-    <row r="75" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O74" s="9"/>
+    </row>
+    <row r="75" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A75" s="1" t="s">
         <v>103</v>
       </c>
@@ -4076,8 +4192,9 @@
       <c r="N75" s="9">
         <v>2017</v>
       </c>
-    </row>
-    <row r="76" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O75" s="9"/>
+    </row>
+    <row r="76" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A76" s="1" t="s">
         <v>104</v>
       </c>
@@ -4118,8 +4235,9 @@
       <c r="N76" s="9">
         <v>2017</v>
       </c>
-    </row>
-    <row r="77" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O76" s="9"/>
+    </row>
+    <row r="77" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A77" s="1" t="s">
         <v>105</v>
       </c>
@@ -4160,8 +4278,9 @@
       <c r="N77" s="9">
         <v>2017</v>
       </c>
-    </row>
-    <row r="78" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O77" s="9"/>
+    </row>
+    <row r="78" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A78" s="1" t="s">
         <v>106</v>
       </c>
@@ -4202,8 +4321,9 @@
       <c r="N78" s="9">
         <v>2013</v>
       </c>
-    </row>
-    <row r="79" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O78" s="9"/>
+    </row>
+    <row r="79" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A79" s="1" t="s">
         <v>107</v>
       </c>
@@ -4244,8 +4364,9 @@
       <c r="N79" s="9">
         <v>2013</v>
       </c>
-    </row>
-    <row r="80" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O79" s="9"/>
+    </row>
+    <row r="80" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A80" s="1" t="s">
         <v>108</v>
       </c>
@@ -4262,7 +4383,7 @@
         <v>0.04</v>
       </c>
       <c r="F80" s="10">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="G80" s="10">
         <v>13.9</v>
@@ -4286,8 +4407,12 @@
       <c r="N80" s="9">
         <v>2017</v>
       </c>
-    </row>
-    <row r="81" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O80" s="9"/>
+      <c r="P80" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="81" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A81" s="1" t="s">
         <v>109</v>
       </c>
@@ -4328,8 +4453,9 @@
       <c r="N81" s="9">
         <v>2017</v>
       </c>
-    </row>
-    <row r="82" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O81" s="9"/>
+    </row>
+    <row r="82" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A82" s="1" t="s">
         <v>110</v>
       </c>
@@ -4370,8 +4496,9 @@
       <c r="N82" s="9">
         <v>2017</v>
       </c>
-    </row>
-    <row r="83" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O82" s="9"/>
+    </row>
+    <row r="83" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A83" s="1" t="s">
         <v>111</v>
       </c>
@@ -4412,8 +4539,9 @@
       <c r="N83" s="9">
         <v>2017</v>
       </c>
-    </row>
-    <row r="84" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O83" s="9"/>
+    </row>
+    <row r="84" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A84" s="1" t="s">
         <v>112</v>
       </c>
@@ -4454,8 +4582,9 @@
       <c r="N84" s="9">
         <v>2017</v>
       </c>
-    </row>
-    <row r="85" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O84" s="9"/>
+    </row>
+    <row r="85" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A85" s="1" t="s">
         <v>113</v>
       </c>
@@ -4496,8 +4625,9 @@
       <c r="N85" s="9">
         <v>2013</v>
       </c>
-    </row>
-    <row r="86" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O85" s="9"/>
+    </row>
+    <row r="86" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A86" s="1" t="s">
         <v>114</v>
       </c>
@@ -4540,8 +4670,9 @@
       <c r="N86" s="9">
         <v>2009</v>
       </c>
-    </row>
-    <row r="87" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O86" s="9"/>
+    </row>
+    <row r="87" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A87" s="1" t="s">
         <v>115</v>
       </c>
@@ -4584,8 +4715,9 @@
       <c r="N87" s="9">
         <v>2008</v>
       </c>
-    </row>
-    <row r="88" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O87" s="9"/>
+    </row>
+    <row r="88" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A88" s="1" t="s">
         <v>116</v>
       </c>
@@ -4628,9 +4760,10 @@
       <c r="N88" s="9">
         <v>2008</v>
       </c>
+      <c r="O88" s="9"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N88" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:P88" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>